--- a/quizzes/012_self_discovery_questionnaire_template--quizzes.xlsx
+++ b/quizzes/012_self_discovery_questionnaire_template--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are your strengths?</t>
+          <t>Strength 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>goal_1_goal</t>
+          <t>goal_1_goal_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>What is your primary goal?</t>
+          <t>Goal 1 Goal 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Self-awareness skills</t>
+          <t>Self Awareness 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>What are your strengths?</t>
+          <t>Self Awareness 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Self-awareness skills</t>
+          <t>Self Awareness 4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What are your strengths?</t>
+          <t>Strength 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What motivates you to take action?</t>
+          <t>Motivation 7</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>What motivates you to achieve your goals?</t>
+          <t>Motivation 8</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>goal_1_goal_choices</t>
+          <t>goal_1_goal_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>goal_1_goal_choices</t>
+          <t>goal_1_goal_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>goal_1_goal_choices</t>
+          <t>goal_1_goal_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
